--- a/Okta.xlsx
+++ b/Okta.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1290821C-6D83-4794-B977-32307D453B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE98D0B-ABC5-43FA-8168-C08C6BD44D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pin" sheetId="1" r:id="rId1"/>
     <sheet name="smaphone" sheetId="2" r:id="rId2"/>
+    <sheet name="一回目" sheetId="3" r:id="rId3"/>
+    <sheet name="2回目" sheetId="4" r:id="rId4"/>
+    <sheet name="③回目" sheetId="5" r:id="rId5"/>
+    <sheet name="カスタム" sheetId="6" r:id="rId6"/>
+    <sheet name="任意" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1121,6 +1126,862 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>449078</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>76918</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD2BFB2-EC50-6024-0BE6-8D11545F0218}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10050278" cy="5144218"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>648652</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>67695</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4CAEBB8-A5DB-1658-C74F-4B6F001A3BF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5791200"/>
+          <a:ext cx="6820852" cy="7306695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>200914</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>172535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2183CAF-7809-8D69-EA37-C9DD2E1B0B08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13935075"/>
+          <a:ext cx="6373114" cy="7773485"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>115369</xdr:colOff>
+      <xdr:row>168</xdr:row>
+      <xdr:rowOff>10638</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09AF0043-8C70-7695-5EFF-DEA03571D4FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="22440900"/>
+          <a:ext cx="7659169" cy="7973538"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>170</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>515379</xdr:colOff>
+      <xdr:row>214</xdr:row>
+      <xdr:rowOff>124954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27037A81-B0D5-AB67-DFE0-F0F26E084CB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="30765750"/>
+          <a:ext cx="7373379" cy="8087854"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>218</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>620169</xdr:colOff>
+      <xdr:row>260</xdr:row>
+      <xdr:rowOff>29640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="图片 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EFD9DD61-4834-B0E2-E20B-D331B9448BBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="39452550"/>
+          <a:ext cx="7478169" cy="7630590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>220158</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>124878</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="图片 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EAC5E4C-591B-E1E7-60FB-122A19B7EBDA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="47777400"/>
+          <a:ext cx="7763958" cy="7544853"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>309</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>658370</xdr:colOff>
+      <xdr:row>352</xdr:row>
+      <xdr:rowOff>124928</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="图片 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28150E86-04E0-85C2-EE3F-60CB3BF74447}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="55921275"/>
+          <a:ext cx="8202170" cy="7906853"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>659231</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>58219</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F22FEA76-403F-C98E-505A-94B563D480DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="14375231" cy="7659169"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>163958</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>20038</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC5A7A21-939E-D2F4-A689-6D0ACBC9AA92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="9048750"/>
+          <a:ext cx="14565758" cy="7078063"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>668470</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>172535</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02FCE101-AFEF-4214-F378-F0CF55EA1FC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12327070" cy="7773485"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>268364</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>162958</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{556A65BA-E5AC-424A-D719-FC073B3FB7F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="8505825"/>
+          <a:ext cx="11926964" cy="7401958"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>156</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>601116</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>10562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF92EE58-3293-2F25-0BFB-C9C3F14AF9A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="28232100"/>
+          <a:ext cx="7459116" cy="7430537"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>201</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>363053</xdr:colOff>
+      <xdr:row>241</xdr:row>
+      <xdr:rowOff>48642</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22E39AFC-D534-9E59-7808-FDB705560126}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="36375975"/>
+          <a:ext cx="7906853" cy="7287642"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>486105</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>29258</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="图片 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CEA24070-126F-D2DA-67A0-515B0742D538}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="180975" y="16849725"/>
+          <a:ext cx="2362530" cy="4896533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>277987</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>153179</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEB8E390-3866-84B7-CC89-2F5C846DDA9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12622387" cy="5582429"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>553580</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>105623</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82BAF3BA-482F-E12D-D51C-6A7B7DA63737}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="6515100"/>
+          <a:ext cx="8097380" cy="6077798"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>525001</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>86747</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58EC2B07-8E94-7161-4FA5-8E367502EEAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13211175"/>
+          <a:ext cx="8068801" cy="7325747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>534527</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>29716</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{453C8F45-260C-1D81-D58C-DE9C1F5A200A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="20993100"/>
+          <a:ext cx="8078327" cy="8173591"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1620,4 +2481,59 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C96582-AD69-4D9C-B16A-B3737E63A02B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCD6F129-467D-4054-958D-38EB338AE407}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B92C82B-3145-4BD4-BD43-0761E149E0DF}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5930F7C7-3644-49F3-A77B-2A6F1AD666BA}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDADA46B-6A12-4327-BD68-70052046E3E0}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>